--- a/output/Data and Chart Outputs/bosnia_herzegovina_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/bosnia_herzegovina_power_generation_daily.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bosnia and Herzegovina power generation by type (ENTSO-E) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -185,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -213,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$70</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -241,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$70</f>
+              <f>'Chart'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -269,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$70</f>
+              <f>'Chart'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -297,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$70</f>
+              <f>'Chart'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -325,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$70</f>
+              <f>'Chart'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -353,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$70</f>
+              <f>'Chart'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -888,7 +889,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:46 UTC; 2079 days, 2021-01-01 to 2026-10-02</t>
+          <t>2026-10-28 00:44 UTC; 2104 days, 2021-01-01 to 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -903,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1785,22 +1786,22 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B34" t="n">
-        <v>81.3009</v>
+        <v>232.9664</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>6.0952</v>
+        <v>8.539399999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.593</v>
+        <v>4.7572</v>
       </c>
       <c r="F34" t="n">
-        <v>327.2066</v>
+        <v>764.0168000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1811,22 +1812,22 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B35" t="n">
-        <v>232.9664</v>
+        <v>509.7733</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>8.539399999999999</v>
+        <v>11.2018</v>
       </c>
       <c r="E35" t="n">
-        <v>4.7572</v>
+        <v>2.4768</v>
       </c>
       <c r="F35" t="n">
-        <v>764.0168000000001</v>
+        <v>674.1935</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1837,22 +1838,22 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B36" t="n">
-        <v>509.7733</v>
+        <v>611.087</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>11.2018</v>
+        <v>10.5124</v>
       </c>
       <c r="E36" t="n">
-        <v>2.4768</v>
+        <v>2.4712</v>
       </c>
       <c r="F36" t="n">
-        <v>674.1935</v>
+        <v>666.7526</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1863,22 +1864,22 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B37" t="n">
-        <v>611.087</v>
+        <v>511.2762</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>10.5124</v>
+        <v>20.0102</v>
       </c>
       <c r="E37" t="n">
-        <v>2.4712</v>
+        <v>3.1723</v>
       </c>
       <c r="F37" t="n">
-        <v>666.7526</v>
+        <v>819.8299000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1889,22 +1890,22 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B38" t="n">
-        <v>511.2762</v>
+        <v>441.4999</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>20.0102</v>
+        <v>16.5696</v>
       </c>
       <c r="E38" t="n">
-        <v>3.1723</v>
+        <v>3.3636</v>
       </c>
       <c r="F38" t="n">
-        <v>819.8299000000001</v>
+        <v>698.0586</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1915,22 +1916,22 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B39" t="n">
-        <v>441.4999</v>
+        <v>527.0914</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>16.5696</v>
+        <v>15.0297</v>
       </c>
       <c r="E39" t="n">
-        <v>3.3636</v>
+        <v>4.3777</v>
       </c>
       <c r="F39" t="n">
-        <v>698.0586</v>
+        <v>602.7613</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1941,22 +1942,22 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B40" t="n">
-        <v>527.0914</v>
+        <v>298.626</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>15.0297</v>
+        <v>11.6447</v>
       </c>
       <c r="E40" t="n">
-        <v>4.3777</v>
+        <v>6.519399999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>602.7613</v>
+        <v>545.7894</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1967,22 +1968,22 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B41" t="n">
-        <v>298.626</v>
+        <v>244.0955</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>11.6447</v>
+        <v>11.3579</v>
       </c>
       <c r="E41" t="n">
-        <v>6.519399999999999</v>
+        <v>5.456600000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>545.7894</v>
+        <v>596.2214</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1993,22 +1994,22 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B42" t="n">
-        <v>244.0955</v>
+        <v>309.873</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>11.3579</v>
+        <v>16.274</v>
       </c>
       <c r="E42" t="n">
-        <v>5.456600000000001</v>
+        <v>3.988</v>
       </c>
       <c r="F42" t="n">
-        <v>596.2214</v>
+        <v>582.058</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2019,22 +2020,22 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B43" t="n">
-        <v>309.873</v>
+        <v>270.9532</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>16.274</v>
+        <v>10.9861</v>
       </c>
       <c r="E43" t="n">
-        <v>3.988</v>
+        <v>12.3539</v>
       </c>
       <c r="F43" t="n">
-        <v>582.058</v>
+        <v>699.7256</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2045,22 +2046,22 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B44" t="n">
-        <v>270.9532</v>
+        <v>190.2677</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>10.9861</v>
+        <v>6.6933</v>
       </c>
       <c r="E44" t="n">
-        <v>12.3539</v>
+        <v>10.6816</v>
       </c>
       <c r="F44" t="n">
-        <v>699.7256</v>
+        <v>607.624</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2071,22 +2072,22 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B45" t="n">
-        <v>190.2677</v>
+        <v>157.1088</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>6.6933</v>
+        <v>9.849200000000002</v>
       </c>
       <c r="E45" t="n">
-        <v>10.6816</v>
+        <v>9.665899999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>607.624</v>
+        <v>635.9515</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2097,22 +2098,22 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B46" t="n">
-        <v>157.1088</v>
+        <v>334.0311</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>9.849200000000002</v>
+        <v>6.158600000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>9.665899999999999</v>
+        <v>9.2179</v>
       </c>
       <c r="F46" t="n">
-        <v>635.9515</v>
+        <v>552.5244</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2123,22 +2124,22 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B47" t="n">
-        <v>334.0311</v>
+        <v>293.195</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>6.158600000000001</v>
+        <v>12.4673</v>
       </c>
       <c r="E47" t="n">
-        <v>9.2179</v>
+        <v>6.0988</v>
       </c>
       <c r="F47" t="n">
-        <v>552.5244</v>
+        <v>665.4011999999999</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2149,22 +2150,22 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B48" t="n">
-        <v>293.195</v>
+        <v>429.3949</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>12.4673</v>
+        <v>19.4806</v>
       </c>
       <c r="E48" t="n">
-        <v>6.0988</v>
+        <v>4.7481</v>
       </c>
       <c r="F48" t="n">
-        <v>665.4011999999999</v>
+        <v>893.7963000000001</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2175,22 +2176,22 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B49" t="n">
-        <v>429.3949</v>
+        <v>437.6003</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>19.4806</v>
+        <v>24.9981</v>
       </c>
       <c r="E49" t="n">
-        <v>4.7481</v>
+        <v>5.043600000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>893.7963000000001</v>
+        <v>836.8693000000001</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2201,22 +2202,22 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B50" t="n">
-        <v>437.6003</v>
+        <v>328.8709</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>24.9981</v>
+        <v>12.1694</v>
       </c>
       <c r="E50" t="n">
-        <v>5.043600000000001</v>
+        <v>6.7707</v>
       </c>
       <c r="F50" t="n">
-        <v>836.8693000000001</v>
+        <v>627.8294000000001</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2227,22 +2228,22 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B51" t="n">
-        <v>328.8709</v>
+        <v>470.8139</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>12.1694</v>
+        <v>19.6222</v>
       </c>
       <c r="E51" t="n">
-        <v>6.7707</v>
+        <v>11.3202</v>
       </c>
       <c r="F51" t="n">
-        <v>627.8294000000001</v>
+        <v>625.4993000000001</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2253,22 +2254,22 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B52" t="n">
-        <v>470.8139</v>
+        <v>357.0446</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>19.6222</v>
+        <v>18.1575</v>
       </c>
       <c r="E52" t="n">
-        <v>11.3202</v>
+        <v>14.5158</v>
       </c>
       <c r="F52" t="n">
-        <v>625.4993000000001</v>
+        <v>499.5051</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2279,22 +2280,22 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B53" t="n">
-        <v>357.0446</v>
+        <v>254.6238</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>18.1575</v>
+        <v>13.9601</v>
       </c>
       <c r="E53" t="n">
-        <v>14.5158</v>
+        <v>18.9789</v>
       </c>
       <c r="F53" t="n">
-        <v>499.5051</v>
+        <v>389.8908</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2305,22 +2306,22 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>254.6238</v>
+        <v>236.3367</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>13.9601</v>
+        <v>11.1059</v>
       </c>
       <c r="E54" t="n">
-        <v>18.9789</v>
+        <v>22.8404</v>
       </c>
       <c r="F54" t="n">
-        <v>389.8908</v>
+        <v>450.6872</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2331,22 +2332,22 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B55" t="n">
-        <v>236.3367</v>
+        <v>254.7613</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>11.1059</v>
+        <v>13.8349</v>
       </c>
       <c r="E55" t="n">
-        <v>22.8404</v>
+        <v>21.8264</v>
       </c>
       <c r="F55" t="n">
-        <v>450.6872</v>
+        <v>460.0466</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2357,22 +2358,22 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B56" t="n">
-        <v>254.7613</v>
+        <v>223.6917</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>13.8349</v>
+        <v>10.2657</v>
       </c>
       <c r="E56" t="n">
-        <v>21.8264</v>
+        <v>17.6184</v>
       </c>
       <c r="F56" t="n">
-        <v>460.0466</v>
+        <v>578.7903</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2383,22 +2384,22 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B57" t="n">
-        <v>223.6917</v>
+        <v>174.3504</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>10.2657</v>
+        <v>6.8107</v>
       </c>
       <c r="E57" t="n">
-        <v>17.6184</v>
+        <v>15.2459</v>
       </c>
       <c r="F57" t="n">
-        <v>578.7903</v>
+        <v>553.4186</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2409,22 +2410,22 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B58" t="n">
-        <v>174.3504</v>
+        <v>227.0604</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>6.8107</v>
+        <v>15.6899</v>
       </c>
       <c r="E58" t="n">
-        <v>15.2459</v>
+        <v>10.8534</v>
       </c>
       <c r="F58" t="n">
-        <v>553.4186</v>
+        <v>602.4725999999999</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2435,22 +2436,22 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B59" t="n">
-        <v>227.0604</v>
+        <v>399.0293</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>15.6899</v>
+        <v>17.0608</v>
       </c>
       <c r="E59" t="n">
-        <v>10.8534</v>
+        <v>6.5762</v>
       </c>
       <c r="F59" t="n">
-        <v>602.4725999999999</v>
+        <v>627.8915999999999</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2461,22 +2462,22 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>399.0293</v>
+        <v>496.7479</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>17.0608</v>
+        <v>11.201</v>
       </c>
       <c r="E60" t="n">
-        <v>6.5762</v>
+        <v>7.1153</v>
       </c>
       <c r="F60" t="n">
-        <v>627.8915999999999</v>
+        <v>643.7075</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2487,22 +2488,22 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B61" t="n">
-        <v>496.7479</v>
+        <v>611.1192</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>11.201</v>
+        <v>15.8719</v>
       </c>
       <c r="E61" t="n">
-        <v>7.1153</v>
+        <v>4.8665</v>
       </c>
       <c r="F61" t="n">
-        <v>643.7075</v>
+        <v>582.5411</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2513,22 +2514,22 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B62" t="n">
-        <v>611.1192</v>
+        <v>629.9953</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>15.8719</v>
+        <v>17.9574</v>
       </c>
       <c r="E62" t="n">
-        <v>4.8665</v>
+        <v>6.5947</v>
       </c>
       <c r="F62" t="n">
-        <v>582.5411</v>
+        <v>459.526</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2539,22 +2540,22 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B63" t="n">
-        <v>629.9953</v>
+        <v>534.5586</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>17.9574</v>
+        <v>14.9913</v>
       </c>
       <c r="E63" t="n">
-        <v>6.5947</v>
+        <v>12.9222</v>
       </c>
       <c r="F63" t="n">
-        <v>459.526</v>
+        <v>577.4764</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2565,22 +2566,22 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B64" t="n">
-        <v>534.5586</v>
+        <v>413.6316</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>14.9913</v>
+        <v>15.5407</v>
       </c>
       <c r="E64" t="n">
-        <v>12.9222</v>
+        <v>6.719399999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>577.4764</v>
+        <v>343.7445</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2591,22 +2592,22 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B65" t="n">
-        <v>413.6316</v>
+        <v>263.0474</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>15.5407</v>
+        <v>8.475899999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>6.719399999999999</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>343.7445</v>
+        <v>519.9992</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2617,22 +2618,22 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B66" t="n">
-        <v>263.0474</v>
+        <v>272.6635</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>8.475899999999999</v>
+        <v>3.8095</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>519.9992</v>
+        <v>453.7277</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2643,22 +2644,22 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B67" t="n">
-        <v>272.6635</v>
+        <v>253.8515</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>3.8095</v>
+        <v>5.1303</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>453.7277</v>
+        <v>559.5205999999999</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2669,22 +2670,22 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B68" t="n">
-        <v>253.8515</v>
+        <v>277.7339</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>5.1303</v>
+        <v>3.1129</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>559.5205999999999</v>
+        <v>617.6066999999999</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2695,53 +2696,27 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B69" t="n">
-        <v>277.7339</v>
+        <v>178.3211</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>3.1129</v>
+        <v>6.2544</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>3.353</v>
       </c>
       <c r="F69" t="n">
-        <v>617.6066999999999</v>
+        <v>587.4699000000001</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B70" t="n">
-        <v>178.3211</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>6.2544</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3.353</v>
-      </c>
-      <c r="F70" t="n">
-        <v>587.4699000000001</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2757,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2080"/>
+  <dimension ref="A1:P2105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106747,6 +106722,1256 @@
         <v>23697.3</v>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>4840.2</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>299</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>20806.7</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2081" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="I2081" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="J2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2081" t="n">
+        <v>26498.2</v>
+      </c>
+      <c r="N2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2081" t="n">
+        <v>16231.2</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>4598.1</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>20661.1</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2082" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I2082" t="n">
+        <v>409.9</v>
+      </c>
+      <c r="J2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2082" t="n">
+        <v>25700.9</v>
+      </c>
+      <c r="N2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2082" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2082" t="n">
+        <v>16730</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>6131.6</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>296</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>20789</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2083" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I2083" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="J2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2083" t="n">
+        <v>27616.5</v>
+      </c>
+      <c r="N2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2083" t="n">
+        <v>21954.7</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>5715.8</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>354.6</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>20425.6</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2084" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="I2084" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="J2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2084" t="n">
+        <v>27014.8</v>
+      </c>
+      <c r="N2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2084" t="n">
+        <v>20728.1</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>6351.5</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>20339.4</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2085" t="n">
+        <v>565.9</v>
+      </c>
+      <c r="I2085" t="n">
+        <v>406.5</v>
+      </c>
+      <c r="J2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2085" t="n">
+        <v>27957.6</v>
+      </c>
+      <c r="N2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2085" t="n">
+        <v>18671.2</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>5242</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>23553.9</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>965</v>
+      </c>
+      <c r="I2086" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2086" t="n">
+        <v>30146.3</v>
+      </c>
+      <c r="N2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2086" t="n">
+        <v>21715.6</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2087" t="n">
+        <v>5570.8</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>485</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>22245.4</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>518.4</v>
+      </c>
+      <c r="I2087" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="J2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2087" t="n">
+        <v>29056.2</v>
+      </c>
+      <c r="N2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2087" t="n">
+        <v>20601.2</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>4761.8</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>22528.1</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>719.7</v>
+      </c>
+      <c r="I2088" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="J2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2088" t="n">
+        <v>28093.6</v>
+      </c>
+      <c r="N2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2088" t="n">
+        <v>19341.6</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>3804.4</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>21925</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>746.2</v>
+      </c>
+      <c r="I2089" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="J2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2089" t="n">
+        <v>26573.1</v>
+      </c>
+      <c r="N2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2089" t="n">
+        <v>17871.6</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>8221.4</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>19897.8</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>813.9</v>
+      </c>
+      <c r="I2090" t="n">
+        <v>245.7</v>
+      </c>
+      <c r="J2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2090" t="n">
+        <v>29494.7</v>
+      </c>
+      <c r="N2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2090" t="n">
+        <v>19839.1</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>6935.7</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>20046.2</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>951.2</v>
+      </c>
+      <c r="I2091" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="J2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2091" t="n">
+        <v>28670.1</v>
+      </c>
+      <c r="N2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2091" t="n">
+        <v>19564</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2092" t="n">
+        <v>6184.7</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>18883.2</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>721.5</v>
+      </c>
+      <c r="I2092" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="J2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2092" t="n">
+        <v>26477.9</v>
+      </c>
+      <c r="N2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2092" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2092" t="n">
+        <v>26314.7</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2093" t="n">
+        <v>5908.6</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>21741.9</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>825.4</v>
+      </c>
+      <c r="I2093" t="n">
+        <v>306.6</v>
+      </c>
+      <c r="J2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2093" t="n">
+        <v>29078.9</v>
+      </c>
+      <c r="N2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2093" t="n">
+        <v>26956.8</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>6259.3</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>23860.7</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>694.6</v>
+      </c>
+      <c r="I2094" t="n">
+        <v>279.7</v>
+      </c>
+      <c r="J2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2094" t="n">
+        <v>31104.8</v>
+      </c>
+      <c r="N2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2094" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2094" t="n">
+        <v>24310.9</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>22824.7</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="I2095" t="n">
+        <v>341</v>
+      </c>
+      <c r="J2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2095" t="n">
+        <v>29375.2</v>
+      </c>
+      <c r="N2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2095" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2095" t="n">
+        <v>22609.5</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>5958.8</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>21856.8</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="I2096" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="J2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2096" t="n">
+        <v>28224.1</v>
+      </c>
+      <c r="N2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2096" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2096" t="n">
+        <v>21923.7</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>9232.1</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>19211</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I2097" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="J2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2097" t="n">
+        <v>29168.5</v>
+      </c>
+      <c r="N2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2097" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2097" t="n">
+        <v>24811.3</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>7299.4</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>303</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>20344.2</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>669.3</v>
+      </c>
+      <c r="I2098" t="n">
+        <v>342.4</v>
+      </c>
+      <c r="J2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2098" t="n">
+        <v>28958.3</v>
+      </c>
+      <c r="N2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2098" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2098" t="n">
+        <v>24122.5</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>8778.4</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>289.9</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>20369.6</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>1069.7</v>
+      </c>
+      <c r="I2099" t="n">
+        <v>29</v>
+      </c>
+      <c r="J2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2099" t="n">
+        <v>30536.6</v>
+      </c>
+      <c r="N2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2099" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2099" t="n">
+        <v>26767.5</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>8473.5</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>292.9</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>21735.4</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="I2100" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="J2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2100" t="n">
+        <v>30838.8</v>
+      </c>
+      <c r="N2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2100" t="n">
+        <v>28285.6</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>5978.6</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>24011.8</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>203.7</v>
+      </c>
+      <c r="I2101" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="J2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2101" t="n">
+        <v>30641.9</v>
+      </c>
+      <c r="N2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2101" t="n">
+        <v>23218.5</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>4387.7</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>24542.2</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2102" t="n">
+        <v>678.9</v>
+      </c>
+      <c r="I2102" t="n">
+        <v>217</v>
+      </c>
+      <c r="J2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2102" t="n">
+        <v>29873</v>
+      </c>
+      <c r="N2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2102" t="n">
+        <v>26558.4</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>5447.3</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>22890.2</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="I2103" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="J2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2103" t="n">
+        <v>28720</v>
+      </c>
+      <c r="N2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2103" t="n">
+        <v>22826.5</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>5459.8</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>23292.9</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>759.1</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>283</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2104" t="n">
+        <v>29805.4</v>
+      </c>
+      <c r="N2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2104" t="n">
+        <v>22662.2</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>7168.6</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>22580.9</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>769.9</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>347.3</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2105" t="n">
+        <v>30877.3</v>
+      </c>
+      <c r="N2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2105" t="n">
+        <v>23823.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
